--- a/4 курс/Metrology/606-22_РечукДМ_Лаб4.xlsx
+++ b/4 курс/Metrology/606-22_РечукДМ_Лаб4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Университет\University\4 курс\Metrology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62212541-3899-4E99-80D5-134320EF2802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FE906B-BE78-4B67-9D84-AAA1378D52C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/4 курс/Metrology/606-22_РечукДМ_Лаб4.xlsx
+++ b/4 курс/Metrology/606-22_РечукДМ_Лаб4.xlsx
@@ -8,17 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Университет\University\4 курс\Metrology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FE906B-BE78-4B67-9D84-AAA1378D52C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17EBDCAB-7411-45E9-A0CE-F15D4FC6ED60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -28,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="23">
   <si>
     <t>№</t>
   </si>
@@ -160,11 +174,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -180,6 +195,2991 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Первый мультиметр</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2К2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$R$1:$AA$1</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Замер 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Замер 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Замер 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Замер 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Замер 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Замер 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Замер 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Замер 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Замер 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Замер 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$R$2:$AA$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2.0000000000000018E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.0000000000000231E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.9999999999997868E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.9999999999997868E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.9999999999997868E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.9999999999997868E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.0000000000000018E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.9999999999997868E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0764-49D0-9180-37F8AB8BE628}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$P$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>6К8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$R$1:$AA$1</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Замер 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Замер 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Замер 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Замер 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Замер 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Замер 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Замер 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Замер 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Замер 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Замер 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$R$3:$AA$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>4.9999999999999822E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.0000000000000036E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.0000000000000497E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.9999999999999822E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.0000000000000036E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.9999999999999822E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.9999999999999822E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.0000000000000036E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.0000000000000036E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.9999999999999822E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0764-49D0-9180-37F8AB8BE628}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$P$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>КЧЧОК</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$R$1:$AA$1</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Замер 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Замер 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Замер 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Замер 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Замер 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Замер 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Замер 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Замер 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Замер 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Замер 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$R$4:$AA$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>-2.9000000000000057</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.4000000000000057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.70000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1.2999999999999972</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.40000000000000568</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.70000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-9.9999999999994316E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0764-49D0-9180-37F8AB8BE628}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$P$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>СКФЗ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$R$1:$AA$1</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Замер 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Замер 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Замер 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Замер 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Замер 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Замер 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Замер 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Замер 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Замер 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Замер 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$R$5:$AA$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>-0.29999999999995453</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.20000000000004547</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.29999999999995453</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.20000000000004547</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.20000000000004547</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.10000000000002274</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.10000000000002274</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.29999999999995453</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.39999999999997726</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0764-49D0-9180-37F8AB8BE628}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$P$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>СЧГК</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$R$1:$AA$1</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Замер 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Замер 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Замер 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Замер 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Замер 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Замер 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Замер 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Замер 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Замер 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Замер 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$R$6:$AA$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.59999999999999432</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.20000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.20000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.9999999999994316E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.40000000000000568</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.20000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.20000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.40000000000000568</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.29999999999999716</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-0764-49D0-9180-37F8AB8BE628}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="664354143"/>
+        <c:axId val="664355103"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="664354143"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="664355103"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="664355103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="664354143"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Второй мультиметр</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$P$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2К2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$R$9:$AA$9</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Замер 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Замер 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Замер 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Замер 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Замер 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Замер 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Замер 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Замер 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Замер 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Замер 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$R$10:$AA$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>9.9999999999997868E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9999999999997868E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.9999999999997868E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.0000000000000018E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.9999999999997868E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.9999999999997868E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.9999999999997868E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.0000000000000018E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9BDD-4615-9F05-2E0B6375BB75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$P$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>6К8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$R$9:$AA$9</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Замер 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Замер 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Замер 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Замер 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Замер 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Замер 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Замер 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Замер 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Замер 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Замер 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$R$11:$AA$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>8.9999999999999858E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.0000000000000071E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0000000000000071E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.0000000000000284E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.9999999999997868E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.0000000000000284E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.0000000000000071E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.0000000000000284E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.9999999999999858E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.0000000000000071E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9BDD-4615-9F05-2E0B6375BB75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$P$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>КЧЧОК</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$R$9:$AA$9</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Замер 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Замер 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Замер 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Замер 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Замер 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Замер 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Замер 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Замер 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Замер 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Замер 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$R$12:$AA$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.79999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.29999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.29999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.20000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.20000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.29999999999999716</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.20000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.20000000000000284</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9BDD-4615-9F05-2E0B6375BB75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$P$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>СКФЗ</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$R$9:$AA$9</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Замер 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Замер 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Замер 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Замер 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Замер 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Замер 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Замер 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Замер 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Замер 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Замер 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$R$13:$AA$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.20000000000004547</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.20000000000004547</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.39999999999997726</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.10000000000002274</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.10000000000002274</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.20000000000004547</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.29999999999995453</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.20000000000004547</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.20000000000004547</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-9BDD-4615-9F05-2E0B6375BB75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$P$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>СЧГК</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$R$9:$AA$9</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Замер 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Замер 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Замер 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Замер 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Замер 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Замер 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Замер 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Замер 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Замер 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Замер 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$R$14:$AA$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.70000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.20000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.20000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.59999999999999432</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.20000000000000284</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-9.9999999999994316E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.40000000000000568</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.59999999999999432</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-9BDD-4615-9F05-2E0B6375BB75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="247169983"/>
+        <c:axId val="240137727"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="247169983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="240137727"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="240137727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="247169983"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>179613</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>10886</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>185056</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AB0D209-006F-CC92-9E64-5969B8BF8BB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>587827</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>27213</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>609598</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>32656</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Диаграмма 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8A11B91-69A8-BD90-3EAA-FA4402E8DB39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Лист1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="R1" t="str">
+            <v>Замер 1</v>
+          </cell>
+          <cell r="S1" t="str">
+            <v>Замер 2</v>
+          </cell>
+          <cell r="T1" t="str">
+            <v>Замер 3</v>
+          </cell>
+          <cell r="U1" t="str">
+            <v>Замер 4</v>
+          </cell>
+          <cell r="V1" t="str">
+            <v>Замер 5</v>
+          </cell>
+          <cell r="W1" t="str">
+            <v>Замер 6</v>
+          </cell>
+          <cell r="X1" t="str">
+            <v>Замер 7</v>
+          </cell>
+          <cell r="Y1" t="str">
+            <v>Замер 8</v>
+          </cell>
+          <cell r="Z1" t="str">
+            <v>Замер 9</v>
+          </cell>
+          <cell r="AA1" t="str">
+            <v>Замер 10</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="Q2" t="str">
+            <v>1,5кОМ</v>
+          </cell>
+          <cell r="R2">
+            <v>4.0000000000000036E-2</v>
+          </cell>
+          <cell r="S2">
+            <v>3.0000000000000027E-2</v>
+          </cell>
+          <cell r="T2">
+            <v>2.0000000000000018E-2</v>
+          </cell>
+          <cell r="U2">
+            <v>0</v>
+          </cell>
+          <cell r="V2">
+            <v>-1.0000000000000009E-2</v>
+          </cell>
+          <cell r="W2">
+            <v>1.0000000000000009E-2</v>
+          </cell>
+          <cell r="X2">
+            <v>-2.0000000000000018E-2</v>
+          </cell>
+          <cell r="Y2">
+            <v>0</v>
+          </cell>
+          <cell r="Z2">
+            <v>2.0000000000000018E-2</v>
+          </cell>
+          <cell r="AA2">
+            <v>-3.0000000000000027E-2</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="Q3" t="str">
+            <v>56кОМ</v>
+          </cell>
+          <cell r="R3">
+            <v>0.79999999999999716</v>
+          </cell>
+          <cell r="S3">
+            <v>2</v>
+          </cell>
+          <cell r="T3">
+            <v>0.79999999999999716</v>
+          </cell>
+          <cell r="U3">
+            <v>0.5</v>
+          </cell>
+          <cell r="V3">
+            <v>-1.5</v>
+          </cell>
+          <cell r="W3">
+            <v>0.79999999999999716</v>
+          </cell>
+          <cell r="X3">
+            <v>2</v>
+          </cell>
+          <cell r="Y3">
+            <v>0.79999999999999716</v>
+          </cell>
+          <cell r="Z3">
+            <v>-1.5</v>
+          </cell>
+          <cell r="AA3">
+            <v>1.7999999999999972</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="Q4" t="str">
+            <v>31ГОм</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="Q5" t="str">
+            <v>5,1кОМ</v>
+          </cell>
+          <cell r="R5">
+            <v>-2.9999999999999361E-2</v>
+          </cell>
+          <cell r="S5">
+            <v>-6.9999999999999396E-2</v>
+          </cell>
+          <cell r="T5">
+            <v>-0.19999999999999929</v>
+          </cell>
+          <cell r="U5">
+            <v>0.1800000000000006</v>
+          </cell>
+          <cell r="V5">
+            <v>-6.9999999999999396E-2</v>
+          </cell>
+          <cell r="W5">
+            <v>2.0000000000000462E-2</v>
+          </cell>
+          <cell r="X5">
+            <v>-9.9999999999999645E-2</v>
+          </cell>
+          <cell r="Y5">
+            <v>-0.11999999999999922</v>
+          </cell>
+          <cell r="Z5">
+            <v>8.0000000000000071E-2</v>
+          </cell>
+          <cell r="AA5">
+            <v>-4.0000000000000036E-2</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="Q6" t="str">
+            <v>10кОМ</v>
+          </cell>
+          <cell r="R6">
+            <v>0.30000000000000071</v>
+          </cell>
+          <cell r="S6">
+            <v>0.19999999999999929</v>
+          </cell>
+          <cell r="T6">
+            <v>0.15000000000000036</v>
+          </cell>
+          <cell r="U6">
+            <v>0.40000000000000036</v>
+          </cell>
+          <cell r="V6">
+            <v>0.38000000000000078</v>
+          </cell>
+          <cell r="W6">
+            <v>0.22000000000000064</v>
+          </cell>
+          <cell r="X6">
+            <v>0.3100000000000005</v>
+          </cell>
+          <cell r="Y6">
+            <v>0.26999999999999957</v>
+          </cell>
+          <cell r="Z6">
+            <v>0.17999999999999972</v>
+          </cell>
+          <cell r="AA6">
+            <v>0.34999999999999964</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -445,10 +3445,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,8 +3488,48 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2"/>
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -529,8 +3569,58 @@
       <c r="M2" s="1">
         <v>2.21</v>
       </c>
+      <c r="N2" s="2"/>
+      <c r="O2" s="1">
+        <v>1</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="R2" s="1">
+        <f>D2-$Q$2</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="S2" s="1">
+        <f t="shared" ref="S2:AA2" si="0">E2-$Q$2</f>
+        <v>-1.0000000000000231E-2</v>
+      </c>
+      <c r="T2" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U2" s="1">
+        <f t="shared" si="0"/>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" si="0"/>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" si="0"/>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" si="0"/>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="Z2" s="1">
+        <f t="shared" si="0"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" si="0"/>
+        <v>9.9999999999997868E-3</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -570,8 +3660,58 @@
       <c r="M3" s="1">
         <v>6.85</v>
       </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="1">
+        <v>2</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="R3" s="1">
+        <f>D3-$Q$3</f>
+        <v>4.9999999999999822E-2</v>
+      </c>
+      <c r="S3" s="1">
+        <f t="shared" ref="S3:AA3" si="1">E3-$Q$3</f>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="T3" s="1">
+        <f t="shared" si="1"/>
+        <v>6.0000000000000497E-2</v>
+      </c>
+      <c r="U3" s="1">
+        <f t="shared" si="1"/>
+        <v>4.9999999999999822E-2</v>
+      </c>
+      <c r="V3" s="1">
+        <f t="shared" si="1"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" si="1"/>
+        <v>4.9999999999999822E-2</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" si="1"/>
+        <v>4.9999999999999822E-2</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" si="1"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" si="1"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" si="1"/>
+        <v>4.9999999999999822E-2</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -611,8 +3751,58 @@
       <c r="M4" s="1">
         <v>99.9</v>
       </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="1">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>100</v>
+      </c>
+      <c r="R4" s="1">
+        <f>D4-$Q$4</f>
+        <v>-2.9000000000000057</v>
+      </c>
+      <c r="S4" s="1">
+        <f t="shared" ref="S4:AA4" si="2">E4-$Q$4</f>
+        <v>-0.5</v>
+      </c>
+      <c r="T4" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.4000000000000057</v>
+      </c>
+      <c r="U4" s="1">
+        <f t="shared" si="2"/>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="V4" s="1">
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" si="2"/>
+        <v>-1.2999999999999972</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" si="2"/>
+        <v>-0.40000000000000568</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" si="2"/>
+        <v>-0.70000000000000284</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" si="2"/>
+        <v>-9.9999999999994316E-2</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -652,8 +3842,58 @@
       <c r="M5" s="1">
         <v>810.4</v>
       </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="1">
+        <v>4</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>810</v>
+      </c>
+      <c r="R5" s="1">
+        <f>D5-$Q$5</f>
+        <v>-0.29999999999995453</v>
+      </c>
+      <c r="S5" s="1">
+        <f t="shared" ref="S5:AA5" si="3">E5-$Q$5</f>
+        <v>-0.20000000000004547</v>
+      </c>
+      <c r="T5" s="1">
+        <f t="shared" si="3"/>
+        <v>0.29999999999995453</v>
+      </c>
+      <c r="U5" s="1">
+        <f t="shared" si="3"/>
+        <v>0.20000000000004547</v>
+      </c>
+      <c r="V5" s="1">
+        <f t="shared" si="3"/>
+        <v>-0.20000000000004547</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" si="3"/>
+        <v>-0.5</v>
+      </c>
+      <c r="X5" s="1">
+        <f t="shared" si="3"/>
+        <v>0.10000000000002274</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" si="3"/>
+        <v>-0.10000000000002274</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" si="3"/>
+        <v>0.29999999999995453</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" si="3"/>
+        <v>0.39999999999997726</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -693,8 +3933,116 @@
       <c r="M6" s="1">
         <v>79.7</v>
       </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="1">
+        <v>5</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>80</v>
+      </c>
+      <c r="R6" s="1">
+        <f>D6-$Q$6</f>
+        <v>0.59999999999999432</v>
+      </c>
+      <c r="S6" s="1">
+        <f t="shared" ref="S6:AA6" si="4">E6-$Q$6</f>
+        <v>0.20000000000000284</v>
+      </c>
+      <c r="T6" s="1">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U6" s="1">
+        <f t="shared" si="4"/>
+        <v>-0.20000000000000284</v>
+      </c>
+      <c r="V6" s="1">
+        <f t="shared" si="4"/>
+        <v>9.9999999999994316E-2</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" si="4"/>
+        <v>-0.40000000000000568</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" si="4"/>
+        <v>-0.20000000000000284</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" si="4"/>
+        <v>0.20000000000000284</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" si="4"/>
+        <v>0.40000000000000568</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" si="4"/>
+        <v>-0.29999999999999716</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
+    </row>
+    <row r="8" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+      <c r="AA8" s="2"/>
+    </row>
+    <row r="9" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -734,8 +4082,48 @@
       <c r="M9" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -775,8 +4163,58 @@
       <c r="M10" s="1">
         <v>2.2200000000000002</v>
       </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="1">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="R10" s="1">
+        <f>D10-$Q$10</f>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="S10" s="1">
+        <f t="shared" ref="S10:AA10" si="5">E10-$Q$10</f>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="T10" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="1">
+        <f t="shared" si="5"/>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="V10" s="1">
+        <f t="shared" si="5"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" si="5"/>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" si="5"/>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" si="5"/>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" si="5"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
     </row>
-    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -816,8 +4254,58 @@
       <c r="M11" s="1">
         <v>6.88</v>
       </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="1">
+        <v>2</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="R11" s="1">
+        <f>D11-$Q$11</f>
+        <v>8.9999999999999858E-2</v>
+      </c>
+      <c r="S11" s="1">
+        <f t="shared" ref="S11:AA11" si="6">E11-$Q$11</f>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="T11" s="1">
+        <f t="shared" si="6"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="U11" s="1">
+        <f t="shared" si="6"/>
+        <v>7.0000000000000284E-2</v>
+      </c>
+      <c r="V11" s="1">
+        <f t="shared" si="6"/>
+        <v>9.9999999999997868E-3</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" si="6"/>
+        <v>7.0000000000000284E-2</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" si="6"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" si="6"/>
+        <v>7.0000000000000284E-2</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" si="6"/>
+        <v>8.9999999999999858E-2</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" si="6"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
     </row>
-    <row r="12" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>3</v>
       </c>
@@ -857,8 +4345,58 @@
       <c r="M12" s="1">
         <v>100.2</v>
       </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="1">
+        <v>3</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>100</v>
+      </c>
+      <c r="R12" s="1">
+        <f>D12-$Q$12</f>
+        <v>0.79999999999999716</v>
+      </c>
+      <c r="S12" s="1">
+        <f t="shared" ref="S12:AA12" si="7">E12-$Q$12</f>
+        <v>-0.5</v>
+      </c>
+      <c r="T12" s="1">
+        <f t="shared" si="7"/>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="U12" s="1">
+        <f t="shared" si="7"/>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="V12" s="1">
+        <f t="shared" si="7"/>
+        <v>0.20000000000000284</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" si="7"/>
+        <v>0.5</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" si="7"/>
+        <v>-0.20000000000000284</v>
+      </c>
+      <c r="Y12" s="1">
+        <f t="shared" si="7"/>
+        <v>-0.29999999999999716</v>
+      </c>
+      <c r="Z12" s="1">
+        <f t="shared" si="7"/>
+        <v>-0.20000000000000284</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" si="7"/>
+        <v>0.20000000000000284</v>
+      </c>
     </row>
-    <row r="13" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>4</v>
       </c>
@@ -898,8 +4436,58 @@
       <c r="M13" s="1">
         <v>810.2</v>
       </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="1">
+        <v>4</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>810</v>
+      </c>
+      <c r="R13" s="1">
+        <f>D13-$Q$13</f>
+        <v>0.20000000000004547</v>
+      </c>
+      <c r="S13" s="1">
+        <f t="shared" ref="S13:AA13" si="8">E13-$Q$13</f>
+        <v>-0.20000000000004547</v>
+      </c>
+      <c r="T13" s="1">
+        <f t="shared" si="8"/>
+        <v>0.39999999999997726</v>
+      </c>
+      <c r="U13" s="1">
+        <f t="shared" si="8"/>
+        <v>0.10000000000002274</v>
+      </c>
+      <c r="V13" s="1">
+        <f t="shared" si="8"/>
+        <v>-0.10000000000002274</v>
+      </c>
+      <c r="W13" s="1">
+        <f t="shared" si="8"/>
+        <v>0.20000000000004547</v>
+      </c>
+      <c r="X13" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="1">
+        <f t="shared" si="8"/>
+        <v>-0.29999999999995453</v>
+      </c>
+      <c r="Z13" s="1">
+        <f t="shared" si="8"/>
+        <v>-0.20000000000004547</v>
+      </c>
+      <c r="AA13" s="1">
+        <f t="shared" si="8"/>
+        <v>0.20000000000004547</v>
+      </c>
     </row>
-    <row r="14" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>5</v>
       </c>
@@ -938,11 +4526,62 @@
       </c>
       <c r="M14" s="1">
         <v>80.599999999999994</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="1">
+        <v>5</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>80</v>
+      </c>
+      <c r="R14" s="1">
+        <f>D14-$Q$14</f>
+        <v>0.70000000000000284</v>
+      </c>
+      <c r="S14" s="1">
+        <f t="shared" ref="S14:AA14" si="9">E14-$Q$14</f>
+        <v>0.5</v>
+      </c>
+      <c r="T14" s="1">
+        <f t="shared" si="9"/>
+        <v>0.5</v>
+      </c>
+      <c r="U14" s="1">
+        <f t="shared" si="9"/>
+        <v>0.20000000000000284</v>
+      </c>
+      <c r="V14" s="1">
+        <f t="shared" si="9"/>
+        <v>-0.20000000000000284</v>
+      </c>
+      <c r="W14" s="1">
+        <f t="shared" si="9"/>
+        <v>0.59999999999999432</v>
+      </c>
+      <c r="X14" s="1">
+        <f t="shared" si="9"/>
+        <v>0.20000000000000284</v>
+      </c>
+      <c r="Y14" s="1">
+        <f t="shared" si="9"/>
+        <v>-9.9999999999994316E-2</v>
+      </c>
+      <c r="Z14" s="1">
+        <f t="shared" si="9"/>
+        <v>0.40000000000000568</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" si="9"/>
+        <v>0.59999999999999432</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>